--- a/data/received/team_results/first_stage.xlsx
+++ b/data/received/team_results/first_stage.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\중진공35\Desktop\greenzone-analysis\outputs\greenzone1st\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC849ED-0065-4962-AD5C-0961D90A48DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
